--- a/output/vagas.xlsx
+++ b/output/vagas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,524 +456,332 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Desenvolvedor(a) de Software Júnior - IT Credit Risk</t>
+          <t>Programador CNC CAD CAM PowerMill hyperMILL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Banco PAN</t>
+          <t>RH INDUSTRIAL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>São Paulo, SP</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>Diadema - SP</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>A combinar</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>catho</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://br.linkedin.com/jobs/view/desenvolvedor-a-de-software-j%C3%BAnior-it-credit-risk-at-banco-pan-4390945706?position=1&amp;pageNum=0&amp;refId=t%2FEJSfzwNsx12antDJIMvw%3D%3D&amp;trackingId=Z%2Bbhip4WSKUTShJc%2Fq%2FwtA%3D%3D</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Somos o PAN
-Ágeis, flexíveis e criativos, exploramos possibilidades com disposição e desejo de fazer acontecer. Sempre prontos para encarar novos desafios, nutrimos líderes que, além de ter garra, são abertos e empáticos, veem na proximidade das relações, o elo entre cada um.
-Nossa missão, se faz cumprida quando transformamos a vida dos outros através dos nossos conhecimentos. Nossos pilares de cultura, reforçam nossa postura idealizadora e com desejo de fazer acontecer: Intensidade, Inconformismo, Eficiência, Espirito de equipe e Integridade.
-Somos seu aliado financeiro, trazendo soluções inteligentes que ajudam você a alcançar seus objetivos com segurança e confiança.
-Principais desafios:
-Atuar no desenvolvimento de aplicações escaláveis e sustentáveis, alinhadas aos desafios de negócio.
-Construir e evoluir soluções de Backend em .NET
-Garantir a qualidade de código, aplicando boas práticas de engenharia, testes automatizados e documentação técnica.
-Colaborar na definição de arquiteturas e soluções, trazendo sugestões de melhorias contínuas.
-Apoiar na gestão de problemas, incidentes e monitoramento de performance.
-Quais as principais competências para a posição?
-Experiência solida em desenvolvimento de software.
-Domínio em .NET, C# e APIs RESTful.
-Python para desenvolvimento de Glue jobs quando necessário.
-Vivência com AWS (Kubernetes (EKS), Lambda, S3, Glue).
-Experiência em metodologias ágeis (Scrum).
-Diferenciais:
-Experiência em bancos ou fintechs.
-Padrões de projetos (SOLID, Clean Code, Design Patterns).
-Arquitetura de APIs e microsserviços resilientes.
-Conhecimento em bancos de dados relacionais e não relacionais.
-Modelo de atuação: Híbrido (2 dias presencial no escritório e 3 dia de home office)
-Requisitos para participar do processo seletivo Interno do BTG para o PAN.
-Ser funcionário do BTG Pactual há pelo menos 18 meses
-Estar se candidatando para uma posição de mudança lateral
-Aprovação do (a) gestor (a) atual para candidatura interna
-Benefícios:
-Bônus / PLR 🤑
-Vale Refeição 🍔
-Vale Alimentação 🍝
-13º de Vale Alimentação 🤌
-Convênio Médico (internação em apartamento para titular e dependentes) 🏥
-Convênio Odonto/Ortodôntico 😁
-Ambulatório Médico no escritório 🚑
-Telemedicina Dr. Alper (Einstein Conecta) ilimitado. 🩺
-Seguro de Vida ❤
-Descontos em mais de 10 mil farmácias 💊
-4 Sessões de psicoterapia por mês 🤝
-Licença familiar estendida (Responsável 6 meses e corresponsável 30 dias) 👨‍🍼🤱
-Auxílio Creche / Babá 🎒
-AcomPANha (programa de acompanhamento para gestantes) 🫃🤰
-Gympass/Totalpass 💪
-Auxílio tecnologia assistivas (reembolso de 85% para colaboradores com deficiência) 🦻🦽
-Day Off Aniversário 🎉
-Day Off Tempo de Casa 🕛
-Programa de reconhecimento por tempo de casa 🏆
-Programas de desenvolvimento 📚
-Massagem e Auriculoterapia 💆‍♀️💆‍♂️
-Salão de beleza no escritório 💇‍♂️💅
-PAE (Orientação Jurídica, Financeira, Psicológica e Social) 🧑‍🎓
-Portal de descontos em diversos segmentos (Allya) 🤑
-Campanha de vacinação (colaborador e dependente) 💉
-Facilitação no financiamento de veículos (Mediante análise) 🚗
-Cartão de crédito PAN com limite diferenciado (Mediante análise) 💳
-Vale Transporte (desconto de apenas 4%) 🚆
-Assistência Funeral 🤍
-Qualquer dúvida sobre a vaga é só mandar um e-mail no mailing: pessoas.selecao@grupopan.com
-#EXPANDAnoPAN</t>
-        </is>
-      </c>
+          <t>https://www.catho.com.br/vagas/programador-cnc-cad-cam-powermill-hypermill/35651965/</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Analista Logística Junior (Foco em Dados)</t>
+          <t>Desenvolvedor</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bimbo Brasil</t>
+          <t>Empresa Confidencial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>São Paulo, SP</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>São Paulo - SP</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A combinar</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>catho</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://br.linkedin.com/jobs/view/analista-log%C3%ADstica-junior-foco-em-dados-at-bimbo-do-brasil-4392450901?position=3&amp;pageNum=0&amp;refId=t%2FEJSfzwNsx12antDJIMvw%3D%3D&amp;trackingId=fztjMuEu0zbLBpcYcXTfJw%3D%3D</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Descrição
-Aqui prezamos pela igualdade de oportunidade e inclusão da diversidade. Para nós, isso se iguala em gênero e identidade de gênero, religião, PCD's, LGBTQIA+, raça/etnia, idade e o fortalecimento do papel da Mulher. Acreditamos que é muito valioso para nossa Cultura compartilhar ideias e pontos de vista diferentes. Venha fazer parte para continuarmos transformando e alimentando um mundo melhor!
-#ElasSabem #SejaVocê #DeMachosaHomens #EntreRaças #Além #GerAções
-Missão Do Cargo
-﻿Responsável por coletar, organizar, analisar e reportar dados da operação logística da Bimbo Brasil, apoiando a
-construção de indicadores, dashboards e análises que contribuam para a tomada de decisão, visando aumentar a
-visibilidade, eficiência e performance operacional, com atuação ao nível nacional e interação com áreas
-administrativas e operacionais.
-Atividades
-Construir, atualizar e reportar indicadores logísticos (KPIs operacionais), como nível de serviço (OTIF/OTD), produtividade, custos de transporte e acuracidade de dados, garantindo visibilidade contínua da performance para as áreas internas;
-Desenvolver e manter dashboards gerenciais e operacionais da área de logística, assegurando padronização, clareza e confiabilidade das informações;
-Contribuir para a integridade, qualidade e segurança dos dados, apoiando a prevenção de inconsistências que possam impactar as análises;
-Realizar análises descritivas e diagnósticas, gerando informações que apoiem decisões táticas da logística;
-Apoiar áreas operacionais e corporativas com análises voltadas à identificação de problemas, oportunidades e melhoria de resultados;
-Participar de reuniões com times operacionais, apoiando na tradução de necessidades do dia a dia em oportunidades analíticas e demandas para o pipeline de entregas;
-Apoiar o mapeamento de processos logísticos, identificando gargalos e sugerindo indicadores que ampliem a visibilidade e o controle da operação.
-Requesitos Necessários
-Ensino superior completo em Engenharia, Administração, Logística, Estatística, Sistemas de Informação, Economia ou áreas correlatas;
-Conhecimento em indicadores de desempenho (KPIs), relatórios ou rotinas de acompanhamento de resultados;
-Excel intermediário;
-Conhecimento em Power BI, Tableau ou similares, como desenvolvedor;
-Requesitos Desejáveis
-Modelagem de dados e análise preditiva – básico
-Noções de SQL ou linguagens analíticas (ex.: Python)</t>
-        </is>
-      </c>
+          <t>https://www.catho.com.br/vagas/desenvolvedor/36002412/</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DESENVOLVEDOR WEB PL</t>
+          <t>Desenvolvedor de Software</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CAOA</t>
+          <t>Indústria multinacional</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>São Paulo, SP</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Alvorada - RS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>De R$ 3.001,00 a R$ 4.000,00</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>catho</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://br.linkedin.com/jobs/view/desenvolvedor-web-pl-at-grupo-caoa-4390559834?position=4&amp;pageNum=0&amp;refId=t%2FEJSfzwNsx12antDJIMvw%3D%3D&amp;trackingId=IftHrI0w0ZybJbvI78Hb2g%3D%3D</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Desenvolvedor para atuar com foco em soluções baseadas na plataforma Web e Microsoft 365. A pessoa será responsável por apoiar na criação, manutenção e evolução de aplicações, fluxos, APP e sistemas Web, além de contribuir no desenvolvimento de APIs e automações utilizando JavaScript e tecnologias similares.
-Responsabilidades e atribuições
-Apoiar no desenvolvimento e customização de sites e APPs utilizando JavaScript.
-Desenvolver conteúdos interativos e apresentações digitais.
-Participar da análise, desenvolvimento e integração de APIs para automação e comunicação entre sistemas.
-Colaborar na implementação de scripts e automações utilizando JavaScript, Python e outras linguagens pertinentes.
-Participar da análise de requisitos para automação e melhoria de processos.
-Documentar processos, fluxos e soluções implementadas.
-Trabalhar junto ao time de TI e áreas de negócio para identificar oportunidades de inovação.
-Requisitos e qualificações
-Conhecimento em Funções Serverless (Azure Functions e Azure API Management).
-Conhecimento em SQL Server.
-Experiência em HTML, CSS, JavaScript.
-Noções de desenvolvimento e integração de APIs (REST e SOAP).
-Noções de lógica de programação e automação de processos.
-Informações adicionais
-Conheça os nossos benefícios: Assistência médica Assistência Odontologica Seguro de vida Vale Transporte Vale Refeição O local de trabalho para essa posição será: Importante: Todas as vagas também estão abertas para pessoas com deficiência</t>
-        </is>
-      </c>
+          <t>https://www.catho.com.br/vagas/desenvolvedor-de-software/36010303/</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Analista Desenvolvedor Pleno</t>
+          <t>Desenvolvedor Python</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Interplayers</t>
+          <t>ENTRUST IT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>São Paulo, SP</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>São Paulo - SP</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A combinar</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>catho</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://br.linkedin.com/jobs/view/analista-desenvolvedor-pleno-at-interplayers-4393254059?position=5&amp;pageNum=0&amp;refId=t%2FEJSfzwNsx12antDJIMvw%3D%3D&amp;trackingId=XrvSvgKwy70wUEevmOfdkA%3D%3D</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>DESCRIÇÃO
-OBJETIVO DO CARGO
-Responsável por analisar, desenvolver, manter e prestar suporte a sistemas corporativos, com foco nas tecnologias PL/SQL, .NET (C#), ASP e MVC. Atuar em projetos de média complexidade, garantindo a aderência às necessidades do negócio e boas práticas de desenvolvimento.
-Atuação dentro da nossa coliga TopSaúdeHUB.
-Responsabilidades
-Analisar e desenvolver sistemas utilizando PL/SQL para manipulação de dados em bancos relacionais (Oracle, SQL Server etc.);
-Desenvolver e manter aplicações web utilizando .NET Framework/Core, C#, ASP.NET e MVC;
-Realizar correções e melhorias em sistemas existentes, aplicando boas práticas de codificação;
-Participar de reuniões com as áreas de negócio para entendimento de demandas;
-Elaborar documentação técnica e de sistemas;
-Realizar testes unitários e de integração;
-Apoiar a equipe de suporte e atender chamados de segundo nível;
-Garantir a integridade e a segurança das informações manipuladas pelos sistemas;
-Requisitos Técnicos
-Experiência sólida com PL/SQL (Oracle, preferencialmente);
-Conhecimento avançado em .NET Framework/Core e linguagem C#;
-Experiência com ASP.NET, MVC, e desenvolvimento de aplicações web;
-Conhecimentos em Web Services (REST/SOAP) e APIs;
-Familiaridade com controle de versão (GIT, TFS ou similar);
-Desejável: conhecimentos em front-end (HTML, CSS, JavaScript, jQuery).
-Desejável: conhecimentos em sistemas de Saúde;
-Formação
-Ensino superior completo em Ciência da Computação, Sistemas de Informação, Engenharia ou áreas correlatas.
-Regime de contratação de tipo: Efetivo – CLT
-Jornada: Período Integral
-Área e especialização profissional: Informática, TI, Telecomunicações - Programador / Desenvolvedor
-Nível hierárquico: Analista
-REQUISITOS
-Escolaridade Mínima: Ensino Superior
-VALORIZADO
-Tempo de experiência: Entre 3 e 5 anos
-BENEFÍCIOS
-DayOff
-TotalPass
-Assistência odontológica
-Seguro de Vida
-Assistência médica
-VA/VR Flexível
-Aux. Home Office
-DayOff de Aniversário</t>
-        </is>
-      </c>
+          <t>https://www.catho.com.br/vagas/desenvolvedor-python/36007851/</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Desenvolvedor React Junior - Trabalho Remoto</t>
+          <t>Desenvolvedor Python</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>Empresa Confidencial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Guarulhos, SP</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>São Paulo - SP</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A combinar</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>catho</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://br.linkedin.com/jobs/view/desenvolvedor-react-junior-trabalho-remoto-at-bairesdev-4392107455?position=6&amp;pageNum=0&amp;refId=t%2FEJSfzwNsx12antDJIMvw%3D%3D&amp;trackingId=Xxyu%2FZ3xqW%2FUTPQwxbvz1w%3D%3D</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Há mais de 15 anos, a BairesDev® é líder em projetos tecnológicos. Entregamos soluções inovadoras para gigantes como Google e Rolls-Royce e as startups mais inovadoras do Vale do Silício.
-Temos uma equipe diversa de mais de 4.000 profissionais formada pelo Top 1% dos talentos de tecnologia do mundo, trabalhando remotamente em cargos de impacto global.
-Ao se candidatar para este cargo, você está dando o primeiro passo em um processo que vai além do comum. Nosso objetivo é alinhar suas paixões, habilidades, e expectativas às nossas vagas, colocando você no caminho para desenvolver uma carreira de sucesso excepcional.
-Desenvolvedor React Junior na BairesDev
-Junte-se à nossa equipe de desenvolvimento, seja nosso novo Desenvolvedor React Junior. Traga seu conhecimento básico em React, JavaScript e desenvolvimento web. Sua dedicação ao aprimoramento de habilidades e a sua vontade de construir aplicativos web amigáveis também serão valorizadas.
-Suas atribuições:
-- Desenvolver e manter aplicativos React, garantindo a qualidade do código e o atendimento às especificações de design.
-- Identificar e resolver bugs e auxiliar na implementação de testes para tornar o aplicativo mais confiável.
-- Participar de revisões de código para aprender as melhores práticas e contribuir para a manutenção de altos padrões de desenvolvimento.
-- Colaborar efetivamente com membros da equipe, incluindo outros desenvolvedores, designers e gerentes de produto.
-- Aprender continuamente e se manter atualizado sobre React e outras tecnologias front-end relacionadas.
-- Participar ativamente de reuniões de equipe e planejamento de projetos, garantindo a entrega pontual das tarefa
-."Esperamos que você tenha:
-- 1 ano de experiência com React.
-- Bom entendimento de algoritmos básicos e estruturas de dados.
-- Conhecimento básico de sistemas de controle de versão, preferencialmente Git.
-- Capacidade de resolver problemas com eficácia e aprender novas tecnologias rapidamente.
-- Bom nível de inglês.
-Como tornamos seu trabalho (e sua vida) mais fácil:
-- Modalidade 100% remota - trabalhe de qualquer lugar.
-- Excelente remuneração em USD ou na sua moeda local, como preferir.
-- Hardware para você trabalhar de casa.
-- Horários flexíveis - faça seu próprio horário.
-- Licença parental remunerada, férias, e feriados nacionais.
-- Ambiente de trabalho inovador e multicultural.
-- Colabore e aprenda com o Top 1% global dos talentos de cada área.
-- Ambiente de apoio com mentoria, promoções, desenvolvimento de habilidades, e diversas oportunidades de crescimento.
-Junte-se a uma equipe global onde seus talentos excepcionais podem se destacar!</t>
-        </is>
-      </c>
+          <t>https://www.catho.com.br/vagas/desenvolvedor-python/36007885/</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Desenvolvedor de Software</t>
+          <t>Desenvolvedor SAP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hypesoft</t>
+          <t>CSC SERVICOS EMPRESARIAIS LTDA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>São Paulo, SP</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Rio de Janeiro - RJ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A combinar</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>catho</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://br.linkedin.com/jobs/view/desenvolvedor-de-software-at-hypesoft-4396143647?position=8&amp;pageNum=0&amp;refId=t%2FEJSfzwNsx12antDJIMvw%3D%3D&amp;trackingId=7%2BANnkQkcdtzHBSJK0Jdew%3D%3D</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Por que se juntar a nós
-A Hypesoft é uma consultoria global de software que preza pela excelência técnica e inovação tecnológica. Nossa missão é ajudar empresas a alcançar o sucesso por meio de soluções customizadas e tecnologias de ponta. Atendemos desde startups em crescimento até grandes corporações, entregando qualidade e eficiência em escala global.
-Trabalhar na Hypesoft significa ultrapassar limites, desafiar o status quo e colaborar com algumas das mentes mais brilhantes da indústria. Aqui, seu potencial só será limitado pelo tamanho dos seus sonhos. Acreditamos no protagonismo e na construção de uma cultura que valoriza a inovação e o crescimento contínuo, e tornamos isso realidade ao fornecer as ferramentas e o suporte que você precisa para desenvolver sua carreira.
-Engenharia na Hypesoft
-O time de Engenharia é formado por áreas como Dados, Infraestrutura, Segurança e Software. Trabalhamos em squads autônomas, sempre prontas para aprender, compartilhar e melhorar continuamente. Nosso objetivo é construir sistemas robustos e escaláveis que impulsionem o crescimento dos nossos clientes e da própria Hypesoft.
-O que você fará
-Como Desenvolvedor(a) Full Stack Júnior, você atuará em todo o ciclo de vida de produtos digitais, contribuindo tanto no back‑end (Node.js, Python e .NET) quanto no front‑end (React). Você terá mentoria contínua de engenheiros experientes, participará de decisões técnicas e ajudará a transformar requisitos de negócio em funcionalidades que impactam milhares de usuários.
-Responsabilidades
-Desenvolver novas features e correções em aplicações web e serviços de back‑end.
-Trabalhar em colaboração com designers, Product Owners e outros engenheiros para entender requisitos de produto e definir soluções viáveis.
-Escrever código limpo, reutilizável e testável, seguindo boas práticas de engenharia.
-Participar de revisões de código, pair programming e iniciativas de melhoria contínua.
-Criar e manter testes automatizados básicos (unitários e de integração).
-Ajudar a monitorar aplicações em produção, investigando e corrigindo incidentes de baixa complexidade.
-Requisitos
-Pelo menos 1  ano de experiência (profissional ou projetos acadêmicos/independentes) em desenvolvimento de software.
-Conhecimento prático em Node.js ou Python e .NET para back‑end.
-Experiência com React (Tailwind, Shadcn, Redux, etc) para construção de interfaces de usuário.
-Noções de HTML, CSS e TypeScript.
-Familiaridade com Git, APIs REST e boas práticas de versionamento de código.
-Conceitos básicos de bancos de dados relacionais ou NoSQL.
-Vontade de aprender novas tecnologias, receber feedback e evoluir rapidamente.
-Inglês técnico para leitura de documentação.
-Diferenciais
-Uso de n8n ou outras plataformas de automação de fluxos.
-Experimentos com Gen AI (OpenAI, Anthropic, etc.) em projetos pessoais ou profissionais.
-Prática com serviços de nuvem (AWS, Azure ou Google Cloud).
-Conhecimentos de testes de performance ou observabilidade (Prometheus, Grafana, etc.).
-Se você é apaixonado(a) por tecnologia e quer crescer em um ambiente que valoriza autonomia, aprendizado contínuo e impacto real, a Hypesoft é o lugar certo para você. Candidate‑se e venha construir o futuro conosco!</t>
-        </is>
-      </c>
+          <t>https://www.catho.com.br/vagas/desenvolvedor-sap/36002363/</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Desenvolvedor Frontend - React/Next.js</t>
+          <t>Desenvolvedor Salesforce</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pulsati</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>São Paulo, SP</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>São Paulo - SP</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>De R$ 9.001,00 a R$ 10.000,00</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>catho</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://br.linkedin.com/jobs/view/desenvolvedor-frontend-react-next-js-at-pulsati-4392949933?position=9&amp;pageNum=0&amp;refId=t%2FEJSfzwNsx12antDJIMvw%3D%3D&amp;trackingId=cGjQ9u75sSBq5k2ztAERLw%3D%3D</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Venha fazer parte do time Pulsati! 🚀
-Desenvolvemos soluções tecnológicas para empresas de saúde de todos os portes e segmentos.
-O maior ingrediente da PULSATI é o investimento em pessoas voltadas para inovação. Juntos nós temos mais de 30 anos de caminhada nessa trajetória na área da saúde.
-Estamos, desde então, unindo forças por um propósito único, tendo empatia para alcançar resultados coletivos.
-Acreditamos que o fator que irá diferenciar nossa empresa das demais é a importância que damos às pessoas que trabalham conosco. A experiência, as habilidades e as expertises de nossos colaboradores e prestadores de serviços decidirão nosso sucesso no mercado.
-Fazemos isso com agilidade, comprometimento, tecnologia, design e um time qualificado para entregar uma solução de ponta a ponta e integrada com um único ponto de contato.
-Cargo:
-Desenvolver e manter interfaces web modernas e responsivas utilizando React.js, Next.js e TypeScript.
-Implementar integrações com APIs RESTful, garantindo correta comunicação entre frontend e backend.
-Trabalhar na otimização de performance das aplicações, garantindo melhor experiência para o usuário final.
-Aplicar boas práticas de desenvolvimento e Design Patterns, contribuindo para a qualidade e escalabilidade do código.
-Participar da definição e alinhamento de contratos de APIs em conjunto com o time de backend.
-Utilizar Git para versionamento de código, seguindo boas práticas de colaboração como GitFlow.
-Apoiar o processo de build, testes e deploy.
-Requisitos:
-Domínio de TypeScript, React.js e Next.js para desenvolvimento de interfaces modernas e performáticas.
-Experiência na integração com APIs RESTful, realizando consumo e tratamento de dados no frontend.
-Experiência com versionamento de código utilizando Git, seguindo boas práticas como GitFlow.
-Conhecimento prático no uso de Docker e familiaridade com ambientes que utilizam Kubernetes e pipelines de CI/CD.
-Conhecimento de Design Patterns aplicados ao frontend, visando organização, escalabilidade e manutenção do código.</t>
-        </is>
-      </c>
+          <t>https://www.catho.com.br/vagas/desenvolvedor-salesforce/35987654/</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Desenvolvedor(a) .NET Core Júnior</t>
+          <t>Desenvolvedor Python</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Banco PAN</t>
+          <t>TRIUNFANTE BRASIL DISTRIBUIDORA DE ALIMENTOS S.A.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>São Paulo, SP</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Campinas - SP</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A combinar</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>catho</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://br.linkedin.com/jobs/view/desenvolvedor-a-net-core-j%C3%BAnior-at-banco-pan-4390944671?position=10&amp;pageNum=0&amp;refId=t%2FEJSfzwNsx12antDJIMvw%3D%3D&amp;trackingId=IMf6mTSWGpCnGpZhwyplnw%3D%3D</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Somos o PAN
-Ágeis, flexíveis e criativos, exploramos possibilidades com disposição e desejo de fazer acontecer. Sempre prontos para encarar novos desafios, nutrimos líderes que, além de ter garra, são abertos e empáticos, veem na proximidade das relações, o elo entre cada um.
-Nossa missão, se faz cumprida quando transformamos a vida dos outros através dos nossos conhecimentos. Nossos pilares de cultura, reforçam nossa postura idealizadora e com desejo de fazer acontecer: Intensidade, Inconformismo, Eficiência, Espirito de equipe e Integridade.
-Somos seu aliado financeiro, trazendo soluções inteligentes que ajudam você a alcançar seus objetivos com segurança e confiança.
-Sobre a vaga:
-Estamos em busca de um(a) desenvolvedor(a) júnior com interesse em evoluir na carreira e aprender boas práticas de desenvolvimento. O(a) profissional atuará em projetos utilizando .NET Core, aplicando conceitos de orientação a objetos e princípios SOLID, além de trabalhar com fluxos Git em um ambiente colaborativo e ágil.
-Responsabilidades:
-Apoiar no desenvolvimento e manutenção de aplicações em .NET Core.
-Aprender e aplicar conceitos de POO e princípios SOLID sob orientação da equipe.
-Utilizar Git para versionamento e participar de fluxos de integração contínua.
-Contribuir em revisões de código e absorver feedback para evolução técnica.
-Colaborar com a equipe em tarefas de documentação e testes.
-Requisitos:
-Conhecimento básico em C# e .NET Core (projetos acadêmicos ou pessoais são bem-vindos).
-Noções de orientação a objetos.
-Familiaridade inicial com Git e versionamento de código.
-Vontade de aprender e aplicar princípios SOLID.
-Boa comunicação e disposição para trabalhar em equipe.
-Diferenciais:
-Experiência com projetos práticos (estágio, freelances ou open source).
-Conhecimento em bancos de dados relacionais.
-Noções de metodologias ágeis.
-Benefícios do PAN:
-Bônus / PLR 🤑
-Vale Refeição 🍔
-Vale Alimentação 🍝
-13º de Vale Alimentação 🤌
-Convênio Médico (internação em apartamento para titular e dependentes) 🏥
-Convênio Odonto/Ortodôntico 😁
-Ambulatório Médico no escritório 🚑
-Telemedicina Dr. Alper (Einstein Conecta) ilimitado. 🩺
-Seguro de Vida ❤
-Descontos em mais de 10 mil farmácias 💊
-4 Sessões de psicoterapia por mês 🤝
-Licença familiar estendida (Responsável 6 meses e corresponsável 30 dias) 👨‍🍼🤱
-Auxílio Creche / Babá 🎒
-AcomPANha (programa de acompanhamento para gestantes) 🫃🤰
-Wellhub/Totalpass 💪
-Auxílio tecnologia assistivas (reembolso de 85% para colaboradores com deficiência) 🦻🦽
-Day Off de aniversário 🕛
-Programas de desenvolvimento 📚
-Massagem e Auriculoterapia 💆‍♀️💆‍♂️
-Salão de beleza no escritório 💇‍♂️💅
-PAE (Orientação Jurídica, Financeira, Psicológica e Social) 🧑‍🎓
-Portal de descontos em diversos segmentos (Allya) 🤑
-Campanha de vacinação (colaborador e dependente) 💉
-Facilitação no financiamento de veículos (Mediante análise) 🚗
-Cartão de crédito PAN com limite diferenciado (Mediante análise) 💳
-Vale Transporte (desconto de apenas 4%) 🚆
-Assistência Funeral 🤍</t>
-        </is>
-      </c>
+          <t>https://www.catho.com.br/vagas/desenvolvedor-python/35993337/</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Desenvolvedor PHP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>POLITEK</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Novo Hamburgo - RS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A combinar</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>catho</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.catho.com.br/vagas/desenvolvedor-php/35989426/</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Desenvolvedor de Sistemas</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FCTH</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>São Paulo - SP</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A combinar</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>catho</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://www.catho.com.br/vagas/desenvolvedor-de-sistemas/35976164/</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/vagas.xlsx
+++ b/output/vagas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,32 +456,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Programador CNC CAD CAM PowerMill hyperMILL</t>
+          <t>Marceneiro Desenvolvedor</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RH INDUSTRIAL</t>
+          <t>DECORA MOB</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Diadema - SP</t>
+          <t>São Paulo - SP</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A combinar</t>
+          <t>R$ 4.300,00
+                a
+                R$ 4.500,00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>catho</t>
+          <t>infojobs</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.catho.com.br/vagas/programador-cnc-cad-cam-powermill-hypermill/35651965/</t>
+          <t>/vaga-de-marceneiro-desenvolvedor-em-sao-paulo__11495528.aspx</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -489,12 +491,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Desenvolvedor</t>
+          <t>Desenvolvedor Javascript PL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Empresa Confidencial</t>
+          <t>Bencorp Saúde</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -509,279 +511,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>catho</t>
+          <t>infojobs</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.catho.com.br/vagas/desenvolvedor/36002412/</t>
+          <t>/vaga-de-desenvolvedor-javascript-pl-em-sao-paulo__11494651.aspx</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Desenvolvedor de Software</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Indústria multinacional</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Alvorada - RS</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>De R$ 3.001,00 a R$ 4.000,00</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>catho</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://www.catho.com.br/vagas/desenvolvedor-de-software/36010303/</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Desenvolvedor Python</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ENTRUST IT</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>São Paulo - SP</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>A combinar</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>catho</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://www.catho.com.br/vagas/desenvolvedor-python/36007851/</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Desenvolvedor Python</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Empresa Confidencial</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>São Paulo - SP</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>A combinar</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>catho</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>https://www.catho.com.br/vagas/desenvolvedor-python/36007885/</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Desenvolvedor SAP</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CSC SERVICOS EMPRESARIAIS LTDA</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Rio de Janeiro - RJ</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>A combinar</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>catho</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>https://www.catho.com.br/vagas/desenvolvedor-sap/36002363/</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Desenvolvedor Salesforce</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>São Paulo - SP</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>De R$ 9.001,00 a R$ 10.000,00</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>catho</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>https://www.catho.com.br/vagas/desenvolvedor-salesforce/35987654/</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Desenvolvedor Python</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TRIUNFANTE BRASIL DISTRIBUIDORA DE ALIMENTOS S.A.</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Campinas - SP</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>A combinar</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>catho</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>https://www.catho.com.br/vagas/desenvolvedor-python/35993337/</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Desenvolvedor PHP</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>POLITEK</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Novo Hamburgo - RS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>A combinar</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>catho</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>https://www.catho.com.br/vagas/desenvolvedor-php/35989426/</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Desenvolvedor de Sistemas</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>FCTH</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>São Paulo - SP</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>A combinar</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>catho</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>https://www.catho.com.br/vagas/desenvolvedor-de-sistemas/35976164/</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
